--- a/usecase2_demand_forecasting/intermediate/intermediate_model_accuracy_comparison.xlsx
+++ b/usecase2_demand_forecasting/intermediate/intermediate_model_accuracy_comparison.xlsx
@@ -373,7 +373,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>20.1</v>
+        <v>17.2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -381,7 +381,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>18.8</v>
+        <v>15.1</v>
       </c>
     </row>
   </sheetData>
